--- a/data/sce_compartment_curation/mitochondrion_annotations_computational_v2.xlsx
+++ b/data/sce_compartment_curation/mitochondrion_annotations_computational_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YJR031C</t>
+          <t>YKL208W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YOL095C</t>
+          <t>YNL104C</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YHR038W</t>
+          <t>YKL087C</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YGL143C</t>
+          <t>YOR089C</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YJR045C</t>
+          <t>YJL066C</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YMR286W</t>
+          <t>YPL167C</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YOR285W</t>
+          <t>YOR215C</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YPL028W</t>
+          <t>YPL097W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YDR226W</t>
+          <t>YKL026C</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YDR316W</t>
+          <t>YNL130C-A</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YDR462W</t>
+          <t>YPL134C</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YOL033W</t>
+          <t>YDR393W</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YOR017W</t>
+          <t>YOL023W</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YER048W-A</t>
+          <t>YBL099W</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YBR263W</t>
+          <t>YIL094C</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YGL080W</t>
+          <t>YDL085W</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YKL056C</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YGL256W</t>
+          <t>YHR120W</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YPL148C</t>
+          <t>YOR147W</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q0060</t>
+          <t>YOR022C</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YKL016C</t>
+          <t>YOR205C</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YML129C</t>
+          <t>YCR004C</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q0144</t>
+          <t>YMR203W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YDR041W</t>
+          <t>Q0142</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YHR179W</t>
+          <t>YIL134W</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YAL039C</t>
+          <t>YLR281C</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YNL211C</t>
+          <t>YOL027C</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YBL090W</t>
+          <t>YKL029C</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YDR125C</t>
+          <t>YMR287C</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YLR422W</t>
+          <t>YMR158W</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YNL063W</t>
+          <t>YDR538W</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YNR041C</t>
+          <t>YDL168W</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YDL174C</t>
+          <t>YMR110C</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YGR015C</t>
+          <t>YOR386W</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YKL187C</t>
+          <t>YPR067W</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YKL152C</t>
+          <t>YFR049W</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YML086C</t>
+          <t>YBR192W</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YDR079W</t>
+          <t>YML030W</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YER154W</t>
+          <t>YJR104C</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YMR193W</t>
+          <t>YKL003C</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YGR255C</t>
+          <t>YKL132C</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YDR298C</t>
+          <t>YEL061C</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YKL134C</t>
+          <t>YLR446W</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YIL146C</t>
+          <t>YDR204W</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YGR101W</t>
+          <t>YFR053C</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YLR368W</t>
+          <t>YDL033C</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YIL070C</t>
+          <t>YDR322C-A</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YNL180C</t>
+          <t>YNL083W</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YGR112W</t>
+          <t>YNL037C</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YPL188W</t>
+          <t>YLL013C</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YMR256C</t>
+          <t>YNL122C</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YOL071W</t>
+          <t>YNR045W</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YFR045W</t>
+          <t>YNL256W</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YJR135W-A</t>
+          <t>YJL116C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YMR189W</t>
+          <t>YGR052W</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YBL078C</t>
+          <t>YJL133C-A</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YKL029C</t>
+          <t>YHR179W</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YJL166W</t>
+          <t>YBR150C</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YLR203C</t>
+          <t>YJR121W</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YOR266W</t>
+          <t>YDR036C</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YOR221C</t>
+          <t>YGR286C</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YKL027W</t>
+          <t>YNL071W</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YOR222W</t>
+          <t>YKL150W</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YPR098C</t>
+          <t>YNR041C</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YOL140W</t>
+          <t>YPR116W</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YPL083C</t>
+          <t>YPL224C</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YPR113W</t>
+          <t>YDR377W</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YNL213C</t>
+          <t>YKL194C</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YDR120C</t>
+          <t>YDR337W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YDR204W</t>
+          <t>YLR072W</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YDR376W</t>
+          <t>YDR494W</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YHR042W</t>
+          <t>YMR064W</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YJR122W</t>
+          <t>YDR296W</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YMR098C</t>
+          <t>YDR405W</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YOR020C</t>
+          <t>YLR091W</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YOR037W</t>
+          <t>YGR132C</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YML061C</t>
+          <t>Q0017</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YDR377W</t>
+          <t>YLR356W</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YMR150C</t>
+          <t>YJR048W</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YLR090W</t>
+          <t>YPL091W</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YBR227C</t>
+          <t>YMR108W</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YBL045C</t>
+          <t>YNL213C</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YJR073C</t>
+          <t>YMR302C</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YMR241W</t>
+          <t>YOR150W</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YAL010C</t>
+          <t>YER181C</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YKL056C</t>
+          <t>YIL139C</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YLR038C</t>
+          <t>YKL134C</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YPL082C</t>
+          <t>YPL017C</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YDR197W</t>
+          <t>YER078C</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Q0080</t>
+          <t>YMR157C</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YPL107W</t>
+          <t>YDR376W</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YNR001C</t>
+          <t>YCL064C</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YER069W</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YNR020C</t>
+          <t>YHR116W</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YDR381C-A</t>
+          <t>YPL186C</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YOR335C</t>
+          <t>YMR098C</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YJR104C</t>
+          <t>YNL135C</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YCL004W</t>
+          <t>YPL159C</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YJR098C</t>
+          <t>YEL052W</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YNL083W</t>
+          <t>YDR462W</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YIL155C</t>
+          <t>YBL057C</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YPL029W</t>
+          <t>YHR199C</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YDR237W</t>
+          <t>YGR015C</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YDR256C</t>
+          <t>YMR002W</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YML030W</t>
+          <t>YBR204C</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YPR133W-A</t>
+          <t>YLR165C</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YPL215W</t>
+          <t>YFR044C</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YLR390W</t>
+          <t>YBL045C</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YJR101W</t>
+          <t>YKR065C</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YNL200C</t>
+          <t>YHR189W</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YPL091W</t>
+          <t>YLR087C</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YGR021W</t>
+          <t>YIL114C</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YEL059C-A</t>
+          <t>YKL167C</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YPR021C</t>
+          <t>YKR087C</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YBR269C</t>
+          <t>YLR008C</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YGL068W</t>
+          <t>YAL001C</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YOR022C</t>
+          <t>YIL157C</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YHR083W</t>
+          <t>YOR292C</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YIL098C</t>
+          <t>YOR305W</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YNL081C</t>
+          <t>Q0010</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YGR240C</t>
+          <t>YGR046W</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YOR241W</t>
+          <t>Q0110</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YCL064C</t>
+          <t>YPL206C</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YKL194C</t>
+          <t>YMR089C</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YGL253W</t>
+          <t>YIL065C</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YHR135C</t>
+          <t>YFL010C</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YLR067C</t>
+          <t>YMR035W</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YLR369W</t>
+          <t>YNL005C</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YGL219C</t>
+          <t>YIL022W</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YLR139C</t>
+          <t>YNL073W</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YLL009C</t>
+          <t>YNL185C</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YDL181W</t>
+          <t>Q0060</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YOR334W</t>
+          <t>YER183C</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YJR095W</t>
+          <t>YNR058W</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YEL050C</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YMR113W</t>
+          <t>YKL113C</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YKL192C</t>
+          <t>YBL090W</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YJR121W</t>
+          <t>YML054C</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YLR142W</t>
+          <t>YDR513W</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YGL211W</t>
+          <t>YKR070W</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YHR059W</t>
+          <t>YDL069C</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Q0075</t>
+          <t>YNL306W</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YMR302C</t>
+          <t>YDR031W</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YER077C</t>
+          <t>YDR505C</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YER087W</t>
+          <t>YOR196C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YLL013C</t>
+          <t>Q0140</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YKL195W</t>
+          <t>YLR067C</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YBR026C</t>
+          <t>YBR091C</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YLR072W</t>
+          <t>YLR415C</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YER168C</t>
+          <t>YBL059W</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YCR028C-A</t>
+          <t>YPL109C</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YBL030C</t>
+          <t>YNL195C</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YDR232W</t>
+          <t>YGL236C</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YGR076C</t>
+          <t>YOR108W</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YGR183C</t>
+          <t>YIL042C</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YLR201C</t>
+          <t>YBR121C</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YPL063W</t>
+          <t>YIL077C</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YNL177C</t>
+          <t>YMR186W</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YBR047W</t>
+          <t>YIL087C</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YDR049W</t>
+          <t>YLR038C</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YDL044C</t>
+          <t>YOR211C</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YBL057C</t>
+          <t>YGL057C</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YNL130C-A</t>
+          <t>YLR312W-A</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YDL004W</t>
+          <t>YML042W</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YLR289W</t>
+          <t>Q0143</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YGL059W</t>
+          <t>YLR289W</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YKL141W</t>
+          <t>YDR197W</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YJL088W</t>
+          <t>YKL141W</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YLR154W-C</t>
+          <t>YMR062C</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YIR037W</t>
+          <t>YKL187C</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YMR038C</t>
+          <t>YKL162C</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YKR063C</t>
+          <t>YMR060C</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YGR052W</t>
+          <t>YLR426W</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YOL023W</t>
+          <t>YKR036C</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YOR286W</t>
+          <t>YER061C</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YBR044C</t>
+          <t>YGR178C</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YBR244W</t>
+          <t>YGR287C</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YGR207C</t>
+          <t>YPL083C</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YKL132C</t>
+          <t>YIL111W</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YNL037C</t>
+          <t>YDR049W</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YJL046W</t>
+          <t>YDR175C</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YDR185C</t>
+          <t>Q0085</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YOL008W</t>
+          <t>YCR071C</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YHR031C</t>
+          <t>YOR130C</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YBL022C</t>
+          <t>YPL270W</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YGR286C</t>
+          <t>YDL119C</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YHR198C</t>
+          <t>YDR508C</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YHR208W</t>
+          <t>YJR135W-A</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YOL141W</t>
+          <t>YKL055C</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YOR065W</t>
+          <t>YBR122C</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YDL048C</t>
+          <t>YOR354C</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YGR222W</t>
+          <t>YOR125C</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YNL073W</t>
+          <t>YHR091C</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YDR353W</t>
+          <t>YML078W</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YPL040C</t>
+          <t>YNL328C</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YMR118C</t>
+          <t>YJR077C</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YGR178C</t>
+          <t>YLR188W</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YHR080C</t>
+          <t>YNL121C</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YAL048C</t>
+          <t>YKR042W</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YEL052W</t>
+          <t>YBR104W</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YOL027C</t>
+          <t>Q0160</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YPR155C</t>
+          <t>YLR382C</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>YIL124W</t>
+          <t>YGR019W</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YIL111W</t>
+          <t>YKL148C</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YJL104W</t>
+          <t>YNL198C</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YHL032C</t>
+          <t>YMR267W</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YHR001W-A</t>
+          <t>YHR162W</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YPR011C</t>
+          <t>YIR037W</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YIL065C</t>
+          <t>YLR174W</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YJR048W</t>
+          <t>YDR061W</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YOR274W</t>
+          <t>YBR120C</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YOL026C</t>
+          <t>YER080W</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YDL120W</t>
+          <t>YJL062W-A</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YNL135C</t>
+          <t>YLR099C</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YPR067W</t>
+          <t>YOR065W</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YBR035C</t>
+          <t>YNL320W</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YHR117W</t>
+          <t>YJR144W</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YFR049W</t>
+          <t>YDL048C</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YLL018C-A</t>
+          <t>YBL078C</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>YCR046C</t>
+          <t>YPL040C</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YOR136W</t>
+          <t>YML110C</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YKR042W</t>
+          <t>YOR176W</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YBR122C</t>
+          <t>YOL141W</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YLR190W</t>
+          <t>YNL208W</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YIL156W-B</t>
+          <t>YGL068W</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YLR290C</t>
+          <t>YGR084C</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YOR187W</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>YDR405W</t>
+          <t>YNL315C</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>YKR049C</t>
+          <t>YOL042W</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>YBL038W</t>
+          <t>YPR134W</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>YBR192W</t>
+          <t>YLL001W</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>YKR071C</t>
+          <t>YJR060W</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YKL208W</t>
+          <t>YPL041C</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>YHR147C</t>
+          <t>YPL099C</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>YIL051C</t>
+          <t>YAR008W</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>YGL107C</t>
+          <t>YOL096C</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YJR060W</t>
+          <t>YGL104C</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YKL003C</t>
+          <t>YCR046C</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YAL054C</t>
+          <t>YPL215W</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YLR251W</t>
+          <t>YML081C-A</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>YDR538W</t>
+          <t>YDR336W</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YBL059C-A</t>
+          <t>YDR347W</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YPL134C</t>
+          <t>YOR285W</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YFL010C</t>
+          <t>YEL071W</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YNL121C</t>
+          <t>YDR226W</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YDL217C</t>
+          <t>YIL124W</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>YDR033W</t>
+          <t>YEL006W</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>YLR239C</t>
+          <t>YER019W</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>YOR089C</t>
+          <t>YOR090C</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>YPL103C</t>
+          <t>YPL222W</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YPR048W</t>
+          <t>YLR251W</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>YOR374W</t>
+          <t>YNL310C</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YDR119W-A</t>
+          <t>YBL080C</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YML042W</t>
+          <t>YMR301C</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YOL096C</t>
+          <t>YDR326C</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YOR226C</t>
+          <t>YOR037W</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YPL078C</t>
+          <t>YCL040W</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YIL134W</t>
+          <t>YGR082W</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YDL178W</t>
+          <t>YAL039C</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>YJL066C</t>
+          <t>YML021C</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>YPL109C</t>
+          <t>YPL118W</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>YGL064C</t>
+          <t>YBR056W</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YKR006C</t>
+          <t>YPR058W</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Q0140</t>
+          <t>YMR286W</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>YNL052W</t>
+          <t>YER026C</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YGR171C</t>
+          <t>YJR016C</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YBR208C</t>
+          <t>YLR454W</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>YDR487C</t>
+          <t>YDL107W</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>YBR106W</t>
+          <t>YOL077W-A</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>YHR199C</t>
+          <t>YDR178W</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>YKL162C</t>
+          <t>YHR011W</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>YNR036C</t>
+          <t>YLR109W</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>YLR164W</t>
+          <t>YIL051C</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YAR035W</t>
+          <t>YJL096W</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>YHR076W</t>
+          <t>YDL078C</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YKL087C</t>
+          <t>YMR113W</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>YMR060C</t>
+          <t>YGL143C</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>YNL252C</t>
+          <t>YLR193C</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>YDR234W</t>
+          <t>YGL136C</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>YDL033C</t>
+          <t>YGR110W</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YBR146W</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>YFL018C</t>
+          <t>YMR188C</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>YNL274C</t>
+          <t>YCR024C</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>YLR043C</t>
+          <t>Q0032</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>YLR304C</t>
+          <t>YNL239W</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Q0115</t>
+          <t>YOR221C</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>YIL094C</t>
+          <t>YPR020W</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>YMR056C</t>
+          <t>YNL081C</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>YMR152W</t>
+          <t>YPL262W</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>YGR031W</t>
+          <t>YHR051W</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>YAL015C</t>
+          <t>YNL130C</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>YGR287C</t>
+          <t>YFL046W</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>YLR355C</t>
+          <t>YLR163C</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>YKR016W</t>
+          <t>YJL112W</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>YPL186C</t>
+          <t>YJR113C</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>YCR003W</t>
+          <t>YGL211W</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>YIL125W</t>
+          <t>YJR101W</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>YHR162W</t>
+          <t>YBL064C</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>YKR085C</t>
+          <t>YDR155C</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>YDR027C</t>
+          <t>YPR097W</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>YLR382C</t>
+          <t>YOR045W</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>YOR205C</t>
+          <t>YKL120W</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>YER058W</t>
+          <t>YLR058C</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>YLR446W</t>
+          <t>YCR003W</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>YOL043C</t>
+          <t>YLL018C-A</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>YGR192C</t>
+          <t>YEL024W</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>YAL044C</t>
+          <t>YPR125W</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>YJL023C</t>
+          <t>YBR047W</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>YNL292W</t>
+          <t>YBR238C</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>YPR033C</t>
+          <t>YKL084W</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>YBR037C</t>
+          <t>YMR030W</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>YDR282C</t>
+          <t>YDR219C</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>YER078C</t>
+          <t>YNL223W</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>YLR312W-A</t>
+          <t>YBR262C</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>YER019W</t>
+          <t>YMR024W</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>YNR016C</t>
+          <t>YKL170W</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>YOR040W</t>
+          <t>YPL060W</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>YIR021W</t>
+          <t>YLR059C</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>YDR375C</t>
+          <t>YNR017W</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>YER132C</t>
+          <t>YER077C</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>YHR011W</t>
+          <t>YDR381C-A</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>YPL159C</t>
+          <t>YNL169C</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>YPR006C</t>
+          <t>YNR018W</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>YDL168W</t>
+          <t>YHR168W</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>YKL067W</t>
+          <t>Q0050</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>YML110C</t>
+          <t>YDR019C</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>YPL017C</t>
+          <t>YPR155C</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>YJR034W</t>
+          <t>YFR033C</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>YDR115W</t>
+          <t>YGR215W</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>YIR024C</t>
+          <t>YMR256C</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>YOR045W</t>
+          <t>YKR071C</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>YLR091W</t>
+          <t>YHR063C</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>YMR225C</t>
+          <t>YPR061C</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>YMR228W</t>
+          <t>YGR062C</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>YLR348C</t>
+          <t>YJR080C</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>YKR052C</t>
+          <t>YOR346W</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Q0085</t>
+          <t>YHR070W</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>YKL137W</t>
+          <t>YML010W</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>YOR305W</t>
+          <t>YDR514C</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>YJR144W</t>
+          <t>YMR145C</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>YML010W</t>
+          <t>YKL195W</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Q0065</t>
+          <t>YMR225C</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>YPL118W</t>
+          <t>YDR041W</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>YPL168W</t>
+          <t>YGR031W</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>YLR415C</t>
+          <t>YPR024W</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>YBL098W</t>
+          <t>YMR194C-B</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Q0010</t>
+          <t>YHR100C</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>YLR059C</t>
+          <t>YBR085W</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>YML081C-A</t>
+          <t>YDL004W</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>YKL167C</t>
+          <t>YNL211C</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>YBR176W</t>
+          <t>YDL217C</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>YPL060W</t>
+          <t>YNL055C</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>YOR354C</t>
+          <t>YMR177W</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>YNL036W</t>
+          <t>YNR007C</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>YDR305C</t>
+          <t>YPL196W</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>YBR120C</t>
+          <t>YDL001W</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>YPR099C</t>
+          <t>YDR375C</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>YGL104C</t>
+          <t>YNR020C</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>YGR082W</t>
+          <t>YPR151C</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>YJL133C-A</t>
+          <t>YJL161W</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>YIL136W</t>
+          <t>YPL107W</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>YDR236C</t>
+          <t>YDR065W</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>YNR074C</t>
+          <t>YHR194W</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>YMR089C</t>
+          <t>YGR021W</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>YLR342W</t>
+          <t>YKR016W</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>YNL310C</t>
+          <t>YDR119W-A</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Q0297</t>
+          <t>YGL084C</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>YKR036C</t>
+          <t>YDR148C</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>YGR257C</t>
+          <t>YOR100C</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>YFL046W</t>
+          <t>YPR117W</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>YGL129C</t>
+          <t>YBR176W</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>YNL284C</t>
+          <t>YOL143C</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>YPR020W</t>
+          <t>YNL252C</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>YDL142C</t>
+          <t>YKR085C</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>YDR516C</t>
+          <t>YNL177C</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>YDR379C-A</t>
+          <t>YNL063W</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>YOR100C</t>
+          <t>YJR148W</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>YDR175C</t>
+          <t>YMR066W</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Q0120</t>
+          <t>YFR011C</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>YOR108W</t>
+          <t>YPL218W</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>YJR080C</t>
+          <t>YLR369W</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>YPL097W</t>
+          <t>YNL200C</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>YPR151C</t>
+          <t>YFR045W</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>YMR207C</t>
+          <t>YNL305C</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>YGR231C</t>
+          <t>YDR234W</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>YBR230C</t>
+          <t>YOL009C</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>YPL013C</t>
+          <t>YDL226C</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>YCL057C-A</t>
+          <t>YHL038C</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>YGL041W-A</t>
+          <t>YHR024C</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>YDR258C</t>
+          <t>YLR190W</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>YJL096W</t>
+          <t>YPR098C</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>YER080W</t>
+          <t>YPR113W</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>YGR235C</t>
+          <t>YIL125W</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>YDR219C</t>
+          <t>YDL066W</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>YGR132C</t>
+          <t>YJL102W</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>YDL045W-A</t>
+          <t>YKL053C-A</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>YIL093C</t>
+          <t>YBR106W</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>YLR132C</t>
+          <t>YMR228W</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>YPR081C</t>
+          <t>YGL256W</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>YLR356W</t>
+          <t>YHR002W</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>YGR008C</t>
+          <t>YFL018C</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>YMR064W</t>
+          <t>YNR036C</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>YDR514C</t>
+          <t>YDL130W-A</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>YER073W</t>
+          <t>YLL007C</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>YML025C</t>
+          <t>YMR038C</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>YPR125W</t>
+          <t>YDL142C</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>YJL143W</t>
+          <t>YOR074C</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>YNL005C</t>
+          <t>YIL006W</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Q0182</t>
+          <t>YGL245W</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>YKL055C</t>
+          <t>YHR080C</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>YJR113C</t>
+          <t>YDR232W</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>YGL063W</t>
+          <t>YOL026C</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>YBR185C</t>
+          <t>YDR033W</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>YOR201C</t>
+          <t>YDR516C</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Q0142</t>
+          <t>YOR236W</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>YKL011C</t>
+          <t>YPL252C</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>YOR150W</t>
+          <t>YDR332W</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>YGR033C</t>
+          <t>YDR305C</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>YDR116C</t>
+          <t>YHR003C</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>YKL155C</t>
+          <t>YOL053W</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>YPR058W</t>
+          <t>YKR066C</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>YDR231C</t>
+          <t>YKL085W</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>YHR005C-A</t>
+          <t>YLR390W</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>YNL208W</t>
+          <t>YOR271C</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>YMR194C-B</t>
+          <t>YDR316W</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>YPL271W</t>
+          <t>YAL010C</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>YCR024C</t>
+          <t>YLR253W</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>YDR322W</t>
+          <t>YMR207C</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>YIL043C</t>
+          <t>Q0255</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>YDL149W</t>
+          <t>YJL166W</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>YBR147W</t>
+          <t>YPR166C</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>YDR393W</t>
+          <t>YLR239C</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>YKL053C-A</t>
+          <t>Q0055</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>YMR003W</t>
+          <t>YIL043C</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>YDL130W-A</t>
+          <t>YNL052W</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>YML007C-A</t>
+          <t>YCL017C</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>YDL001W</t>
+          <t>YAR035W</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>YGL085W</t>
+          <t>YER132C</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>YBL099W</t>
+          <t>YLR295C</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>YBR204C</t>
+          <t>YPL063W</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>YOL059W</t>
+          <t>YOR251C</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>YHR155W</t>
+          <t>YOL071W</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>YBR150C</t>
+          <t>YER017C</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>YHR116W</t>
+          <t>YPR100W</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>YNL100W</t>
+          <t>YBR039W</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Q0250</t>
+          <t>YHL004W</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>YDR493W</t>
+          <t>YJR100C</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>YMR023C</t>
+          <t>YBL015W</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>YNL003C</t>
+          <t>YFL036W</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Q0143</t>
+          <t>YGL253W</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>YOR020W-A</t>
+          <t>YGL187C</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>YEL020W-A</t>
+          <t>YMR083W</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>YOR074C</t>
+          <t>YDR268W</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>YNL168C</t>
+          <t>YGR207C</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>YJR051W</t>
+          <t>YLR368W</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>YLR295C</t>
+          <t>YDR511W</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>YLR089C</t>
+          <t>YPL132W</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Q0045</t>
+          <t>YKR063C</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>YGL228W</t>
+          <t>YDL157C</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>YHR003C</t>
+          <t>YGR076C</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>YDL119C</t>
+          <t>YGR231C</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>YLR259C</t>
+          <t>YML007C-A</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>YMR282C</t>
+          <t>YNL295W</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>YNL104C</t>
+          <t>YJR045C</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>YKR087C</t>
+          <t>YHR147C</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>YGL057C</t>
+          <t>YOR228C</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>YDL215C</t>
+          <t>YJL143W</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>YML032C</t>
+          <t>YOL043C</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>YFR048W</t>
+          <t>YDL202W</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>YPR097W</t>
+          <t>YFL042C</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>YGL221C</t>
+          <t>YJL208C</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>YOR142W</t>
+          <t>YOR232W</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>YPR047W</t>
+          <t>YER048W-A</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>YNL195C</t>
+          <t>YOL095C</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>YDR511W</t>
+          <t>YGL226W</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Q0050</t>
+          <t>YJL147C</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>YMR188C</t>
+          <t>YPL078C</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>YHL038C</t>
+          <t>YDL067C</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>YBR039W</t>
+          <t>YML032C</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>YPR117W</t>
+          <t>YLR154W-C</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>YDR513W</t>
+          <t>YFL016C</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>YKL120W</t>
+          <t>YBR282W</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>YNL009W</t>
+          <t>YDR236C</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>YGR169C</t>
+          <t>YER154W</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>YGR029W</t>
+          <t>YMR189W</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>YJR148W</t>
+          <t>YOR004W</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Q0032</t>
+          <t>YDR125C</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>YFR011C</t>
+          <t>YHR106W</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>YMR108W</t>
+          <t>YHR031C</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>YKR064W</t>
+          <t>YPR047W</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>YDL107W</t>
+          <t>YGR222W</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>YBR146W</t>
+          <t>YOL033W</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>YER004W</t>
+          <t>YOR356W</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>YHL021C</t>
+          <t>YHR076W</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>YNR017W</t>
+          <t>YHR017W</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>YBL059W</t>
+          <t>YOR374W</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>YGR084C</t>
+          <t>YHR038W</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>YGR220C</t>
+          <t>YMR257C</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>YGR244C</t>
+          <t>YDR237W</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>YLR168C</t>
+          <t>YNR037C</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>YPR134W</t>
+          <t>YIR024C</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>YAL001C</t>
+          <t>YBL030C</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>YDR430C</t>
+          <t>YER086W</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>YJL109C</t>
+          <t>YBR244W</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>YAL056W</t>
+          <t>YPR184W</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>YLR174W</t>
+          <t>YLR283W</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>YLR283W</t>
+          <t>YEL039C</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Q0070</t>
+          <t>YLR218C</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>YBR024W</t>
+          <t>YGL197W</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>YDR332W</t>
+          <t>YNR001C</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>YOL077W-A</t>
+          <t>YOR201C</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>YBL095W</t>
+          <t>YBL059C-A</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>YBR104W</t>
+          <t>YBR185C</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>YKL157W</t>
+          <t>YER182W</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>YLR109W</t>
+          <t>YGL080W</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>YML091C</t>
+          <t>YGR147C</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>YOR158W</t>
+          <t>YIR021W</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>YGR165W</t>
+          <t>YGR008C</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>YOR232W</t>
+          <t>YCL057C-A</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>YKL026C</t>
+          <t>YPL172C</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>YLL040C</t>
+          <t>YEL030W</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>YOL053W</t>
+          <t>YMR056C</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>YGR236C</t>
+          <t>YOR222W</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>YPL167C</t>
+          <t>YDL027C</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>YMR287C</t>
+          <t>YGR171C</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>YGL018C</t>
+          <t>YOR297C</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>YIL114C</t>
+          <t>YGR257C</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>YDR268W</t>
+          <t>YLR142W</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>YOR004W</t>
+          <t>YLR393W</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>YCR012W</t>
+          <t>YPL188W</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>YHR002W</t>
+          <t>YBL098W</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>YLR008C</t>
+          <t>YDL198C</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>YPL270W</t>
+          <t>YDR493W</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>YKR065C</t>
+          <t>YBR268W</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>YKR070W</t>
+          <t>YPL059W</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>YJL180C</t>
+          <t>YDR058C</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>YLR099C</t>
+          <t>YIL160C</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Q0160</t>
+          <t>YLR203C</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>YDL067C</t>
+          <t>YIL156W-B</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>YGL191W</t>
+          <t>YOL008W</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>YHR120W</t>
+          <t>YOR136W</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>YGL020C</t>
+          <t>YKL138C</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>YPR184W</t>
+          <t>YBL022C</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>YPR037C</t>
+          <t>YNR074C</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>YFL036W</t>
+          <t>YGR240C</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>YJL208C</t>
+          <t>YBR147W</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>YDR178W</t>
+          <t>YER053C</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>YGR110W</t>
+          <t>YCR028C-A</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>YGR046W</t>
+          <t>YNL292W</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>YOR251C</t>
+          <t>YNL168C</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>YGL226W</t>
+          <t>YDR298C</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>YHL004W</t>
+          <t>YGR165W</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>YHR037W</t>
+          <t>YJR085C</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>YDR326C</t>
+          <t>YPR006C</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>YMR205C</t>
+          <t>YPR048W</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>YER182W</t>
+          <t>YOR020C</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>YBR268W</t>
+          <t>YER178W</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>YDR470C</t>
+          <t>YCR083W</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>YFR044C</t>
+          <t>YJL003W</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>YDL085W</t>
+          <t>YGR094W</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>YPR001W</t>
+          <t>YOL059W</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>YNL137C</t>
+          <t>Q0080</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>YNL256W</t>
+          <t>YNR022C</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>YBR003W</t>
+          <t>YKR064W</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>YKL113C</t>
+          <t>YJL178C</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>YDL078C</t>
+          <t>YGL129C</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>YBR179C</t>
+          <t>YAL048C</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>YOL129W</t>
+          <t>YBL038W</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>YJR003C</t>
+          <t>YDL164C</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>YJL003W</t>
+          <t>YMR023C</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>YEL039C</t>
+          <t>YDL215C</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>YKL150W</t>
+          <t>YPR081C</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>YMR257C</t>
+          <t>YKL040C</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Q0110</t>
+          <t>YKL106W</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>YBR056W</t>
+          <t>YKL155C</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>YJL045W</t>
+          <t>YOR040W</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>YBR251W</t>
+          <t>YOL140W</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>YDL036C</t>
+          <t>YOR274W</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>YFR033C</t>
+          <t>YOR330C</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>YMR158W</t>
+          <t>YKR049C</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>YOR215C</t>
+          <t>YBR026C</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>YDR036C</t>
+          <t>YBR227C</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>YMR110C</t>
+          <t>YDL181W</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>YHR017W</t>
+          <t>YPR004C</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>YJR085C</t>
+          <t>YNL003C</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>YOL009C</t>
+          <t>YOR142W</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>YML008C</t>
+          <t>YHR155W</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>YDL226C</t>
+          <t>YAL015C</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>YBR121C</t>
+          <t>YNR016C</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>YDR322C-A</t>
+          <t>YBR179C</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>YML009C</t>
+          <t>YMR306W</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>YLR165C</t>
+          <t>YER038W-A</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>YDR155C</t>
+          <t>YGL020C</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>YGR062C</t>
+          <t>YGR244C</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>YOR176W</t>
+          <t>YLR168C</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>YPL262W</t>
+          <t>YNL137C</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>YLR426W</t>
+          <t>YJR003C</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Q0055</t>
+          <t>YML129C</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YJL131C</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>YLR099W-A</t>
+          <t>YPR021C</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>YCL040W</t>
+          <t>YGR193C</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>YMR306W</t>
+          <t>YGR235C</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>YNL306W</t>
+          <t>YER058W</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>YER050C</t>
+          <t>YJR051W</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>YGR215W</t>
+          <t>YKL152C</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>YBR262C</t>
+          <t>YKL192C</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>YJR016C</t>
+          <t>YER087W</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>YMR115W</t>
+          <t>YDR256C</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>YNL026W</t>
+          <t>YER170W</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>YER183C</t>
+          <t>YJR034W</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>YDR505C</t>
+          <t>YER140W</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>YJL126W</t>
+          <t>YLL041C</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>YHL014C</t>
+          <t>YGR255C</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>YMR211W</t>
+          <t>YMR205C</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>YPR024W</t>
+          <t>YCL004W</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>YDR196C</t>
+          <t>YPL103C</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>YIL087C</t>
+          <t>Q0250</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>YKL148C</t>
+          <t>Q0115</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>YPR100W</t>
+          <t>YDR529C</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>YBR091C</t>
+          <t>YGL041W-A</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>YPL104W</t>
+          <t>YGL064C</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>YNL223W</t>
+          <t>YHR042W</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>YGR094W</t>
+          <t>YLR164W</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>YKL040C</t>
+          <t>YIL146C</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>YMR166C</t>
+          <t>YLR346C</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>YLR193C</t>
+          <t>YJL180C</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>YBL064C</t>
+          <t>YGR174C</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>YDR508C</t>
+          <t>YDR185C</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>YER141W</t>
+          <t>YDL045W-A</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>YHR189W</t>
+          <t>Q0105</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>YLR204W</t>
+          <t>YLR348C</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>YHR063C</t>
+          <t>YDR322W</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>YOR356W</t>
+          <t>YKL027W</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>YPL041C</t>
+          <t>YGL107C</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>YIL157C</t>
+          <t>YLR077W</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>YJL133W</t>
+          <t>YBR163W</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>YLR188W</t>
+          <t>YML061C</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>YML054C</t>
+          <t>YHR208W</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>YER181C</t>
+          <t>Q0092</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>YGR088W</t>
+          <t>YGL119W</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>YPL173W</t>
+          <t>YGR029W</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>YCL017C</t>
+          <t>YJL127C-B</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>YBL013W</t>
+          <t>Q0120</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>YJL147C</t>
+          <t>YJL109C</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>YPL224C</t>
+          <t>YMR293C</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>YLR253W</t>
+          <t>YDR120C</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>YHR070W</t>
+          <t>YKL016C</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>YPL172C</t>
+          <t>YNL070W</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>YMR177W</t>
+          <t>YPR133W-A</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>YBL080C</t>
+          <t>YDR079W</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>YKL170W</t>
+          <t>YKR052C</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>YAL044W-A</t>
+          <t>YEL059C-A</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>YPL206C</t>
+          <t>YNL026W</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>YKL114C</t>
+          <t>YBR230C</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>YKL085W</t>
+          <t>YMR097C</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>YCL044C</t>
+          <t>YPL271W</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>YKL084W</t>
+          <t>YMR118C</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>YMR301C</t>
+          <t>YHL032C</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>YOL143C</t>
+          <t>YBL013W</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>YOR228C</t>
+          <t>YHR059W</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>YPL132W</t>
+          <t>YDR115W</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>YJL161W</t>
+          <t>YGL085W</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>YJL200C</t>
+          <t>YGR033C</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>YGR147C</t>
+          <t>YDR116C</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>YCR004C</t>
+          <t>YGR220C</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>YLL041C</t>
+          <t>YKL213C</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>YOL042W</t>
+          <t>YOL129W</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>YDL066W</t>
+          <t>YDL120W</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>YIL042C</t>
+          <t>YGR096W</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>YLR393W</t>
+          <t>YOR241W</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>YHR008C</t>
+          <t>YPR140W</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>YFL016C</t>
+          <t>YBR044C</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>YLR163C</t>
+          <t>YPR033C</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>YER178W</t>
+          <t>YHL021C</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>YDR341C</t>
+          <t>YBR208C</t>
         </is>
       </c>
     </row>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>YLR087C</t>
+          <t>YLR090W</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>YNL055C</t>
+          <t>YPL029W</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>YDR336W</t>
+          <t>Q0070</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>YER026C</t>
+          <t>YMR059W</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>YPR140W</t>
+          <t>YPL082C</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>YMR059W</t>
+          <t>YDL104C</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>YJL102W</t>
+          <t>YDR438W</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>YEL061C</t>
+          <t>YKL093W</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>YER140W</t>
+          <t>YGL221C</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>YER014W</t>
+          <t>YJL060W</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>YMR002W</t>
+          <t>YMR193W</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Q0092</t>
+          <t>YBR003W</t>
         </is>
       </c>
     </row>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>YFL042C</t>
+          <t>YMR152W</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>YHR067W</t>
+          <t>YNL274C</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>YDR494W</t>
+          <t>YBR269C</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>YKR066C</t>
+          <t>YPL005W</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>YNR045W</t>
+          <t>YDL178W</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Q0130</t>
+          <t>YER050C</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>YOR196C</t>
+          <t>YIL093C</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>YNL122C</t>
+          <t>YJL063C</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>YOR297C</t>
+          <t>YGR192C</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>YDL131W</t>
+          <t>YER141W</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>YOR271C</t>
+          <t>YLR089C</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>YER170W</t>
+          <t>YBR251W</t>
         </is>
       </c>
     </row>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>YJL127C-B</t>
+          <t>YGL228W</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>YCR071C</t>
+          <t>YML086C</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>YLL007C</t>
+          <t>YJL045W</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>YIL022W</t>
+          <t>YGR088W</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>YGR243W</t>
+          <t>YKR079C</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>YDL069C</t>
+          <t>YJR098C</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>YML078W</t>
+          <t>YBR035C</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>YDL027C</t>
+          <t>YKL067W</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>YER153C</t>
+          <t>YHR083W</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>YKR079C</t>
+          <t>YDL036C</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>YNR058W</t>
+          <t>Q0065</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>YJL071W</t>
+          <t>YDR379C-A</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>YFR053C</t>
+          <t>YER014W</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>YKL106W</t>
+          <t>YOR335C</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>YDR194C</t>
+          <t>Q0275</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>YER017C</t>
+          <t>YDR070C</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>YOR236W</t>
+          <t>YPL135W</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>YHR091C</t>
+          <t>YBR024W</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>YBR282W</t>
+          <t>YHL014C</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>YJL054W</t>
+          <t>YPR001W</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>YOR125C</t>
+          <t>YCL044C</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Q0275</t>
+          <t>YEL020W-A</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>YEL024W</t>
+          <t>YHR037W</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>YPR116W</t>
+          <t>YPR099C</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>YPL099C</t>
+          <t>YER153C</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>YKL037W</t>
+          <t>YMR072W</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>YHR051W</t>
+          <t>YAL044W-A</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>YMR035W</t>
+          <t>YGL191W</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>YNR018W</t>
+          <t>YDR350C</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>YIL139C</t>
+          <t>YDR282C</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>YGR150C</t>
+          <t>YAL056W</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>YDL202W</t>
+          <t>YML009C</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>YPL005W</t>
+          <t>YLR342W</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>YEL030W</t>
+          <t>YJL071W</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>YNL198C</t>
+          <t>YAL044C</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>YDR061W</t>
+          <t>YGR183C</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>YMR244C-A</t>
+          <t>YMR003W</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>YER061C</t>
+          <t>YDL174C</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>YMR024W</t>
+          <t>YGL219C</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>YGR019W</t>
+          <t>Q0045</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>YGR193C</t>
+          <t>YDR258C</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>YDR148C</t>
+          <t>YMR244C-A</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>YML120C</t>
+          <t>YGR150C</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>YAL046C</t>
+          <t>YOR286W</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>YIL160C</t>
+          <t>YGR028W</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>YPL059W</t>
+          <t>YNL009W</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>YPR166C</t>
+          <t>YOL021C</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>YJL131C</t>
+          <t>YBR084W</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>YHR168W</t>
+          <t>YML025C</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>YDR347W</t>
+          <t>YIL070C</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>YPL183W-A</t>
+          <t>YGL059W</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>YMR072W</t>
+          <t>YHR067W</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>YNL070W</t>
+          <t>YLR389C</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>YJR077C</t>
+          <t>YHR135C</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>YNL295W</t>
+          <t>YLR139C</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>YOR330C</t>
+          <t>YPL183W-A</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>YAR008W</t>
+          <t>YLR395C</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>YEL050C</t>
+          <t>YDR194C</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>YHR194W</t>
+          <t>YBR221C</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>YPL135W</t>
+          <t>YMR115W</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>YGR181W</t>
+          <t>YCL009C</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>YHR024C</t>
+          <t>YBR263W</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>YGL245W</t>
+          <t>YDR470C</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>YLR218C</t>
+          <t>YJR122W</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>YDR337W</t>
+          <t>YHR198C</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>YLL027W</t>
+          <t>YIL155C</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>YMR186W</t>
+          <t>YKL137W</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>YBR084W</t>
+          <t>YLR105C</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>YGL197W</t>
+          <t>Q0130</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>YGR102C</t>
+          <t>Q0182</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>YDR019C</t>
+          <t>YER004W</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>YNL130C</t>
+          <t>YMR282C</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>YPL218W</t>
+          <t>YJL200C</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>YNL315C</t>
+          <t>YDR487C</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>YLR346C</t>
+          <t>YER073W</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>YDR529C</t>
+          <t>YGR101W</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>YNL071W</t>
+          <t>YIR004W</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>YPL189C-A</t>
+          <t>YHR008C</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>YBR291C</t>
+          <t>YPR037C</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>YLR281C</t>
+          <t>YLR290C</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>YOR386W</t>
+          <t>YLR043C</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>YBR085W</t>
+          <t>YPL168W</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>YLR058C</t>
+          <t>YLR132C</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>YPR061C</t>
+          <t>YKR006C</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Q0255</t>
+          <t>YDL131W</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>YDR296W</t>
+          <t>YGR169C</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>YGR096W</t>
+          <t>YBR037C</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>YEL071W</t>
+          <t>YJL104W</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>YKL093W</t>
+          <t>YPL013C</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>YGL136C</t>
+          <t>YLL040C</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>YLR105C</t>
+          <t>YLR099W-A</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>YPR191W</t>
+          <t>YPL028W</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>YER057C</t>
+          <t>YGR112W</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>YGL236C</t>
+          <t>YPR191W</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>YDR350C</t>
+          <t>YJL088W</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>YHR106W</t>
+          <t>YFR048W</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>YBR163W</t>
+          <t>YML120C</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>YLR454W</t>
+          <t>YGR102C</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>YBL107C</t>
+          <t>YHR117W</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>YER086W</t>
+          <t>YMR166C</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>YML021C</t>
+          <t>YOR020W-A</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>YBR221C</t>
+          <t>YJR095W</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>YJL060W</t>
+          <t>YAL054C</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>YDL198C</t>
+          <t>YLR439W</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>YLR069C</t>
+          <t>YJL054W</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>YMR145C</t>
+          <t>YDR196C</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>YMR157C</t>
+          <t>YMR211W</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>YNL131W</t>
+          <t>YJR073C</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>YNR007C</t>
+          <t>YLL009C</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>YDL104C</t>
+          <t>YDR430C</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>YMR203W</t>
+          <t>YNL180C</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>YMR267W</t>
+          <t>YBL107C</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>YGR028W</t>
+          <t>YKL094W</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>YNL169C</t>
+          <t>YMR241W</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>YGL187C</t>
+          <t>YLR201C</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>YDR065W</t>
+          <t>YPL148C</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>YLL001W</t>
+          <t>YKL037W</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>YPL222W</t>
+          <t>YGR243W</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>YPR004C</t>
+          <t>YCR012W</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>YLR439W</t>
+          <t>YGR012W</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>YER038W-A</t>
+          <t>YKL114C</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>YCR083W</t>
+          <t>YKL157W</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>YDL164C</t>
+          <t>Q0144</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Q0105</t>
+          <t>YOR334W</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>YGR174C</t>
+          <t>YHR001W-A</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>YOR147W</t>
+          <t>YDL044C</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>YCR079W</t>
+          <t>YJL046W</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>YDL157C</t>
+          <t>YPL104W</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>YIL077C</t>
+          <t>YLR204W</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>YMR066W</t>
+          <t>YPL173W</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>YEL006W</t>
+          <t>YDR341C</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>YER069W</t>
+          <t>YGL063W</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>YLR395C</t>
+          <t>YDR027C</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Q0017</t>
+          <t>YDR353W</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>YPL196W</t>
+          <t>YJL023C</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>YMR293C</t>
+          <t>YNL131W</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>YJR100C</t>
+          <t>YGR181W</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>YMR083W</t>
+          <t>YOR158W</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>YIR004W</t>
+          <t>YOR226C</t>
         </is>
       </c>
     </row>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>YDR058C</t>
+          <t>YGL018C</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>YER053C</t>
+          <t>YIL136W</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>YJL112W</t>
+          <t>YJR031C</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>YGL119W</t>
+          <t>YML091C</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>YNL328C</t>
+          <t>YLR422W</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>YNR037C</t>
+          <t>YHR005C-A</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>YKL213C</t>
+          <t>Q0075</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>YLR389C</t>
+          <t>YLR304C</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>YMR097C</t>
+          <t>YDR231C</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>YNR022C</t>
+          <t>YML008C</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>YKL138C</t>
+          <t>YDL149W</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>YOR090C</t>
+          <t>YJL133W</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>YPL252C</t>
+          <t>YOR266W</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>YDR031W</t>
+          <t>YER168C</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>YKL094W</t>
+          <t>YNL100W</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>YMR030W</t>
+          <t>YAL046C</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>YJL062W-A</t>
+          <t>YGR236C</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>YCL009C</t>
+          <t>YJL126W</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>YDR070C</t>
+          <t>YER057C</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>YIL006W</t>
+          <t>YNL284C</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>YGR012W</t>
+          <t>YNL036W</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>YOR130C</t>
+          <t>YBR291C</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>YOR211C</t>
+          <t>YLR069C</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>YBR238C</t>
+          <t>YKL011C</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>YJL063C</t>
+          <t>YIL098C</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>YHR100C</t>
+          <t>YLR355C</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>YNL239W</t>
+          <t>YLL027W</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>YBL015W</t>
+          <t>YMR150C</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>YOR346W</t>
+          <t>YPR011C</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>YGL084C</t>
+          <t>YLR259C</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>YNL185C</t>
+          <t>YCR079W</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>YOR187W</t>
+          <t>Q0297</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>YMR062C</t>
+          <t>YBL095W</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>YLR077W</t>
+          <t>YPL189C-A</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>YOL021C</t>
+          <t>YOR017W</t>
         </is>
       </c>
     </row>
